--- a/discovery-engine/audit/audit_sample.xlsx
+++ b/discovery-engine/audit/audit_sample.xlsx
@@ -560,8 +560,16 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
@@ -590,7 +598,11 @@
 cues_remembered: ['people_present']</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
     </row>
@@ -620,8 +632,16 @@
 cues_remembered: ['none_stated']</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
@@ -650,8 +670,16 @@
 cues_remembered: ['text_content']</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="78" customHeight="1">
@@ -680,7 +708,11 @@
 cues_remembered: ['visual_detail']</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
     </row>
@@ -710,7 +742,11 @@
 cues_remembered: ['approx_time']</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
     </row>
@@ -740,8 +776,16 @@
 cues_remembered: ['none_stated']</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="65" customHeight="1">
@@ -770,7 +814,11 @@
 cues_remembered: ['text_content']</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
     </row>
@@ -800,7 +848,11 @@
 cues_remembered: ['none_stated']</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
     </row>
@@ -830,8 +882,16 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
@@ -860,8 +920,16 @@
 cues_remembered: ['context_event']</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="104" customHeight="1">
@@ -890,7 +958,11 @@
 cues_remembered: ['people_present']</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
     </row>
@@ -920,8 +992,16 @@
 cues_remembered: ['approx_time', 'source_channel']</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="H15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="52" customHeight="1">
@@ -950,7 +1030,11 @@
 cues_remembered: ['approx_time']</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
     </row>
@@ -980,7 +1064,11 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
     </row>
@@ -1010,7 +1098,11 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
     </row>
@@ -1040,7 +1132,11 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
     </row>
@@ -1070,8 +1166,16 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="150" customHeight="1">
@@ -1100,7 +1204,11 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
     </row>
@@ -1130,7 +1238,11 @@
 cues_remembered: []</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
     </row>
